--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -716,16 +716,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -802,16 +820,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-4.9</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -884,16 +920,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>0.9</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -901,16 +955,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>4.476</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1052,16 +1124,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>41.243</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bank of Zambia</t>
+          <t>Bank of Zambia MPC statement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt stock (~91% of GDP)</t>
+          <t>Total public debt, approximate; domestic T-bills and bonds over 45% of total debt stock</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF (domestic interest payments, nearly 35% of domestic revenue)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jan-26</t>
+          <t>22-Jan-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1015,7 +1011,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves</t>
+          <t>definition not stated in source</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1053,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of Zambia</t>
+          <t>Bank of Zambia (stated as 'over 4.2 months')</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1317,16 +1313,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Concluded 38-month US$1.3bn ECF in Jan-26; negotiating successor program</t>
+          <t>38-month ECF concluded Jan-26 (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1.3</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>31-Aug-22</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MoFNP</t>
+          <t>Ministry of Finance and National Planning</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, approximate; domestic T-bills and bonds over 45% of total debt stock</t>
+          <t>total public debt, approximate, domestic and external; domestic T-bills and bonds over 45% of stock</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>definition not stated in source</t>
+          <t>gross international reserves; composition not stated in source</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of Zambia (stated as 'over 4.2 months')</t>
+          <t>Bank of Zambia (stated as over 4.2 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month ECF concluded Jan-26 (sixth and final review); successor programme under negotiation</t>
+          <t>38-month Extended Credit Facility, completed (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bank of Zambia MPC statement</t>
+          <t>Bank of Zambia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt, approximate, domestic and external; domestic T-bills and bonds over 45% of stock</t>
+          <t>total public debt, approximately, domestic plus external</t>
         </is>
       </c>
     </row>
@@ -880,10 +880,14 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>latest per IMF Jan-26 (approximate; domestic interest as share of domestic revenue)</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMF (domestic interest payments, nearly 35% of domestic revenue)</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1011,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves; composition not stated in source</t>
+          <t>gross, as reported by Bank of Zambia (gold treatment not stated)</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of Zambia (stated as over 4.2 months)</t>
+          <t>Bank of Zambia (document states over 4.2 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1313,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month Extended Credit Facility, completed (sixth and final review); successor programme under negotiation</t>
+          <t>Extended Credit Facility (38-month) concluded Jan-26; successor programme under negotiation</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bank of Zambia</t>
+          <t>Bank of Zambia MPC statement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance and National Planning</t>
+          <t>MoFNP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt, approximately, domestic plus external</t>
+          <t>total public debt, approximate; domestic T-bills and bonds over 45% of stock</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest per IMF Jan-26 (approximate; domestic interest as share of domestic revenue)</t>
+          <t>latest per IMF (approximate; domestic interest as share of domestic revenue)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross, as reported by Bank of Zambia (gold treatment not stated)</t>
+          <t>gross international reserves; composition not specified in source</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of Zambia (document states over 4.2 months)</t>
+          <t>Bank of Zambia (reported as 'over 4.2 months')</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Credit Facility (38-month) concluded Jan-26; successor programme under negotiation</t>
+          <t>38-month ECF completed Jan-26 (sixth and final review); successor programme under negotiation</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MoFNP</t>
+          <t>Ministry of Finance and National Planning</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt, approximate; domestic T-bills and bonds over 45% of stock</t>
+          <t>total public debt (external and domestic), approximate</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest per IMF (approximate; domestic interest as share of domestic revenue)</t>
+          <t>Jan-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -895,7 +895,11 @@
           <t>22-Jan-26</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>domestic interest payments as % of domestic revenue, 'nearly 35%'</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1015,7 +1019,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves; composition not specified in source</t>
+          <t>gross international reserves as reported by BoZ; gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1321,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month ECF completed Jan-26 (sixth and final review); successor programme under negotiation</t>
+          <t>38-month ECF, completed (sixth and final review, US$190m final disbursement); successor programme under negotiation</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bank of Zambia MPC statement</t>
+          <t>Bank of Zambia MPC statement (cut of 250 bps)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt (external and domestic), approximate</t>
+          <t>total public debt (external plus domestic), approximate; domestic T-bills and bonds over 45% of stock</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jan-26</t>
+          <t>latest per IMF ECF final review</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF, Jan-26 (domestic interest payments / domestic revenue, 'nearly 35%'; not total interest)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -895,11 +895,7 @@
           <t>22-Jan-26</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>domestic interest payments as % of domestic revenue, 'nearly 35%'</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1019,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves as reported by BoZ; gold treatment not stated</t>
+          <t>gross international reserves (inclusion of gold not stated)</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of Zambia (reported as 'over 4.2 months')</t>
+          <t>Bank of Zambia (stated as 'over 4.2 months')</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1321,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>38-month ECF, completed (sixth and final review, US$190m final disbursement); successor programme under negotiation</t>
+          <t>Successor programme under negotiation; 38-month US$1.3bn ECF completed Jan-26</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Zambia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Zambia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/zambia.json</t>
         </is>
       </c>
     </row>
